--- a/exports/IQRA_ScaleUp_Cost_Model_Year1.xlsx
+++ b/exports/IQRA_ScaleUp_Cost_Model_Year1.xlsx
@@ -9,12 +9,9 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Team" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CTO Rate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="AI &amp; LLM" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Knowledge" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Infrastructure" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Timeline" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Replit Costs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Your Cost" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Timeline" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65,12 +62,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F2A24"/>
-      <sz val="12"/>
+      <color rgb="00103D2B"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00103D2B"/>
+      <color rgb="001F2A24"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -141,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,7 +147,7 @@
     <xf numFmtId="167" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -163,6 +160,7 @@
     <xf numFmtId="167" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -173,17 +171,15 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -549,14 +545,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -569,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared by the CTO for the founder · Target: 1,000,000+ users &amp; 100,000 books · Currency: BDT (USD shown)</t>
+          <t>Prepared by the CTO · Target: 1,000,000+ users &amp; 100,000 books · Only two costs: Replit + your time</t>
         </is>
       </c>
     </row>
@@ -581,12 +577,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Steady-state annual run-rate (full 1M)</t>
+          <t>Annual run-rate (full 1M scale)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>CTO cost per hour (fully-loaded)</t>
+          <t>Your cost per hour</t>
         </is>
       </c>
     </row>
@@ -596,11 +592,11 @@
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>(Team!G13+'AI &amp; LLM'!B9+Infrastructure!C10+Knowledge!B7)*Assumptions!B5</f>
+        <f>('Replit Costs'!C16+'Your Cost'!B8/Assumptions!B5)*Assumptions!B5</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>'CTO Rate'!B9</f>
+        <f>'Your Cost'!B6</f>
         <v/>
       </c>
     </row>
@@ -610,18 +606,18 @@
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>(Team!G13+'AI &amp; LLM'!B9+Infrastructure!C10+Knowledge!B7)</f>
+        <f>('Replit Costs'!C16+'Your Cost'!B8/Assumptions!B5)</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>'CTO Rate'!B9/Assumptions!B5</f>
+        <f>'Your Cost'!B6/Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Annual cost by category (steady-state run-rate)</t>
+          <t>Annual cost breakdown (run-rate at full scale)</t>
         </is>
       </c>
     </row>
@@ -650,11 +646,11 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Team &amp; salaries</t>
+          <t>Replit — AI / LLM (Claude)</t>
         </is>
       </c>
       <c r="B10" s="11">
-        <f>Team!G13</f>
+        <f>'Replit Costs'!C15</f>
         <v/>
       </c>
       <c r="C10" s="12">
@@ -662,18 +658,18 @@
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>B10/(Team!G13+'AI &amp; LLM'!B9+Infrastructure!C10+Knowledge!B7)</f>
+        <f>B10/('Replit Costs'!C16+'Your Cost'!B8/Assumptions!B5)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>AI / LLM (Claude)</t>
+          <t>Replit — fixed platform (hosting, DB, storage)</t>
         </is>
       </c>
       <c r="B11" s="11">
-        <f>'AI &amp; LLM'!B9</f>
+        <f>'Replit Costs'!C14</f>
         <v/>
       </c>
       <c r="C11" s="12">
@@ -681,18 +677,18 @@
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>B11/(Team!G13+'AI &amp; LLM'!B9+Infrastructure!C10+Knowledge!B7)</f>
+        <f>B11/('Replit Costs'!C16+'Your Cost'!B8/Assumptions!B5)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>You (CTO)</t>
         </is>
       </c>
       <c r="B12" s="11">
-        <f>Infrastructure!C10</f>
+        <f>'Your Cost'!B8/Assumptions!B5</f>
         <v/>
       </c>
       <c r="C12" s="12">
@@ -700,146 +696,127 @@
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>B12/(Team!G13+'AI &amp; LLM'!B9+Infrastructure!C10+Knowledge!B7)</f>
+        <f>B12/('Replit Costs'!C16+'Your Cost'!B8/Assumptions!B5)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Knowledge (storage)</t>
-        </is>
-      </c>
-      <c r="B13" s="11">
-        <f>Knowledge!B7</f>
-        <v/>
-      </c>
-      <c r="C13" s="12">
-        <f>B13*Assumptions!B5</f>
-        <v/>
-      </c>
-      <c r="D13" s="13">
-        <f>B13/(Team!G13+'AI &amp; LLM'!B9+Infrastructure!C10+Knowledge!B7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>TOTAL run-rate</t>
         </is>
       </c>
-      <c r="B14" s="15">
-        <f>SUM(B10:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="16">
-        <f>SUM(C10:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>SUM(D10:D13)</f>
-        <v/>
+      <c r="B13" s="15">
+        <f>SUM(B10:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>SUM(C10:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>SUM(D10:D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Key metrics</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Key metrics</t>
-        </is>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Registered users (target)</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
+        <f>Assumptions!B7</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Registered users (target)</t>
+          <t>Monthly active users</t>
         </is>
       </c>
       <c r="B17" s="18">
-        <f>Assumptions!B7</f>
+        <f>'Replit Costs'!B5</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Monthly active users</t>
+          <t>Chat queries per year</t>
         </is>
       </c>
       <c r="B18" s="18">
-        <f>'AI &amp; LLM'!B4</f>
+        <f>'Replit Costs'!B5*Assumptions!B9*12</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Chat queries per year</t>
+          <t>Books integrated</t>
         </is>
       </c>
       <c r="B19" s="18">
-        <f>'AI &amp; LLM'!B6</f>
+        <f>Assumptions!B16</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Books integrated</t>
+          <t>Knowledge storage (GB)</t>
         </is>
       </c>
       <c r="B20" s="18">
-        <f>Assumptions!B16</f>
+        <f>Assumptions!B16*Assumptions!B17/1024</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Knowledge storage (GB)</t>
-        </is>
-      </c>
-      <c r="B21" s="18">
-        <f>Knowledge!B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Total headcount</t>
-        </is>
-      </c>
-      <c r="B22" s="18">
-        <f>Team!C13</f>
-        <v/>
+          <t>One-time book processing (USD)</t>
+        </is>
+      </c>
+      <c r="B21" s="19">
+        <f>'Replit Costs'!B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>• 'Year-1 total' assumes users grow over 12 months (realistic first-year spend, incl. one-time book processing).</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>• How to read this: 'Year-1 total' assumes users ramp up over 12 months (realistic first-year spend).</t>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>• 'Run-rate' is the annual cost once you are actually at the full 1,000,000-user scale.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>• 'Steady-state run-rate' is the annual cost once you are actually at the full 1,000,000-user scale.</t>
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>• Only two things cost money: Replit (platform + AI) and your time. No other team.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>• Every figure is driven by the Assumptions sheet — change an input there and all totals recompute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>• Biggest cost driver is AI/LLM at scale; see the AI &amp; LLM sheet for levers to reduce it.</t>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>• AI usage is the biggest driver — it depends entirely on how many people chat. Change the Assumptions to see it move.</t>
         </is>
       </c>
     </row>
@@ -854,16 +831,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>IQRA Assistant — Year-1 Scale-Up Cost Model</t>
         </is>
@@ -872,7 +849,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every input below is editable. Totals on all other sheets update automatically.</t>
+          <t>Every input below is editable. All totals on the other sheets update automatically.</t>
         </is>
       </c>
     </row>
@@ -894,13 +871,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="23" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -908,23 +885,23 @@
           <t>USD → BDT exchange rate</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>120</v>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>BDT per 1 USD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Users &amp; Usage (Year-1 target)</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="n"/>
-      <c r="C6" s="22" t="n"/>
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Users &amp; usage (Year-1 target)</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n"/>
+      <c r="C6" s="23" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -932,10 +909,10 @@
           <t>Registered users (target)</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="24" t="n">
         <v>1000000</v>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>users</t>
         </is>
@@ -944,15 +921,15 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Monthly active users (% of registered)</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="n">
+          <t>Monthly active users (% who actually chat each month)</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>% actually chatting each month</t>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -962,34 +939,34 @@
           <t>Avg chat queries per active user / month</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>queries / month</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>AI / LLM (Claude, per query)</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>AI / LLM per query (Claude via Replit AI)</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Input tokens per query (prompt + retrieved context)</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n">
+          <t>Input tokens per query (question + retrieved context)</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
         <v>4000</v>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>tokens</t>
         </is>
@@ -1001,10 +978,10 @@
           <t>Output tokens per query (the answer)</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>700</v>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>tokens</t>
         </is>
@@ -1016,10 +993,10 @@
           <t>LLM input price</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t>USD per 1,000,000 tokens</t>
         </is>
@@ -1031,23 +1008,23 @@
           <t>LLM output price</t>
         </is>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>USD per 1,000,000 tokens</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Knowledge base (100,000 books)</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1055,10 +1032,10 @@
           <t>Books to integrate</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>100000</v>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>books</t>
         </is>
@@ -1070,10 +1047,10 @@
           <t>Average file size per book</t>
         </is>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
@@ -1082,198 +1059,138 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Search chunks generated per book</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="n">
-        <v>137</v>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>chunks (drives DB size)</t>
+          <t>Object-storage price (Replit App Storage)</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>USD per GB / month</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Object-storage price</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>USD per GB / month</t>
+          <t>One-time processing of 100k books (extract + chunk)</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>USD (one-time, month 1)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>One-time ingestion compute (extract + chunk 100k books)</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>USD (one-time, month 1)</t>
-        </is>
-      </c>
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Replit platform (monthly, USD)</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>Team basis (Bangladesh)</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Replit subscription (Core plan)</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>USD / month</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Working days per month</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>days</t>
+          <t>Deployment compute (Autoscale) — tune from Replit usage dashboard</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>USD / month</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Working hours per day</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="C23" s="24" t="inlineStr">
-        <is>
-          <t>hours</t>
+          <t>Database (PostgreSQL)</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>USD / month</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Employer overhead multiplier (benefits, tax, equipment, office)</t>
-        </is>
-      </c>
-      <c r="B24" s="29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>× base salary</t>
-        </is>
-      </c>
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Your cost (CTO — the only person)</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Infrastructure (monthly, USD)</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Your pay per month</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>BDT / month</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>App servers / hosting (autoscale for 1M users)</t>
-        </is>
-      </c>
-      <c r="B26" s="28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>USD / month</t>
+          <t>Working days per month</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>days</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Managed PostgreSQL (scaled; FTS over ~13.7M chunks)</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>USD / month</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>Bandwidth / CDN</t>
-        </is>
-      </c>
-      <c r="B28" s="28" t="n">
-        <v>300</v>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>USD / month</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Transactional email (Resend)</t>
-        </is>
-      </c>
-      <c r="B29" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>USD / month</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Monitoring / logging / error tracking</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="n">
-        <v>200</v>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>USD / month</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Domain, SSL, misc SaaS</t>
-        </is>
-      </c>
-      <c r="B31" s="28" t="n">
-        <v>50</v>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>USD / month</t>
+          <t>Working hours per day</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>hours</t>
         </is>
       </c>
     </row>
@@ -1288,356 +1205,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Team &amp; Salaries (Bangladesh)</t>
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Replit Costs</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Salaries in BDT / month. Annual loaded cost includes the employer overhead multiplier from Assumptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Monthly salary (BDT)</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Monthly total (BDT)</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Annual base (BDT)</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>Annual loaded (BDT)</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>Annual loaded (USD)</t>
+          <t>Replit is the entire platform: hosting, deployment, database, storage, and the AI that powers chat.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Chief Technology Officer (you)</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C4" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="12">
-        <f>B4*C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="12">
-        <f>D4*12</f>
-        <v/>
-      </c>
-      <c r="F4" s="12">
-        <f>E4*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G4" s="11">
-        <f>F4/Assumptions!B5</f>
-        <v/>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>AI usage basis (at full scale)</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>180000</v>
-      </c>
-      <c r="C5" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="12">
-        <f>B5*C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="12">
-        <f>D5*12</f>
-        <v/>
-      </c>
-      <c r="F5" s="12">
-        <f>E5*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>F5/Assumptions!B5</f>
+          <t>Monthly active users (MAU)</t>
+        </is>
+      </c>
+      <c r="B5" s="18">
+        <f>Assumptions!B7*Assumptions!B8</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>160000</v>
-      </c>
-      <c r="C6" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="12">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="12">
-        <f>D6*12</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
-        <f>E6*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
-        <f>F6/Assumptions!B5</f>
+          <t>Queries per month</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>B5*Assumptions!B9</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>DevOps / SRE Engineer</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C7" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="12">
-        <f>B7*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="12">
-        <f>D7*12</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
-        <f>E7*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
-        <f>F7/Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>120000</v>
-      </c>
-      <c r="C8" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12">
-        <f>B8*C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="12">
-        <f>D8*12</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
-        <f>E8*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
-        <f>F8/Assumptions!B5</f>
+          <t>Cost per query (USD)</t>
+        </is>
+      </c>
+      <c r="B7" s="31">
+        <f>Assumptions!B11/1000000*Assumptions!B13+Assumptions!B12/1000000*Assumptions!B14</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Knowledge-Ops Lead</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="12">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="12">
-        <f>D9*12</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
-        <f>E9*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G9" s="11">
-        <f>F9/Assumptions!B5</f>
-        <v/>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Monthly (USD)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Annual (USD)</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Annual (BDT)</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Content Specialist (book curation)</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>3</v>
+          <t>Replit subscription (Core)</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>Assumptions!B21</f>
+        <v/>
+      </c>
+      <c r="C10" s="11">
+        <f>B10*12</f>
+        <v/>
       </c>
       <c r="D10" s="12">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="12">
-        <f>D10*12</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
-        <f>E10*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G10" s="11">
-        <f>F10/Assumptions!B5</f>
+        <f>C10*Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Community / Support</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>80000</v>
-      </c>
-      <c r="C11" s="30" t="n">
-        <v>1</v>
+          <t>Deployment compute (Autoscale)</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>Assumptions!B22</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>B11*12</f>
+        <v/>
       </c>
       <c r="D11" s="12">
-        <f>B11*C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="12">
-        <f>D11*12</f>
-        <v/>
-      </c>
-      <c r="F11" s="12">
-        <f>E11*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>F11/Assumptions!B5</f>
+        <f>C11*Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Product Manager</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>1</v>
+          <t>Database (PostgreSQL)</t>
+        </is>
+      </c>
+      <c r="B12" s="11">
+        <f>Assumptions!B23</f>
+        <v/>
+      </c>
+      <c r="C12" s="11">
+        <f>B12*12</f>
+        <v/>
       </c>
       <c r="D12" s="12">
-        <f>B12*C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="12">
-        <f>D12*12</f>
-        <v/>
-      </c>
-      <c r="F12" s="12">
-        <f>E12*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="G12" s="11">
-        <f>F12/Assumptions!B5</f>
+        <f>C12*Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="31">
-        <f>SUM(C4:C12)</f>
-        <v/>
-      </c>
-      <c r="D13" s="16">
-        <f>SUM(D4:D12)</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>SUM(E4:E12)</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>SUM(F4:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="15">
-        <f>SUM(G4:G12)</f>
-        <v/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Object storage (100k books)</t>
+        </is>
+      </c>
+      <c r="B13" s="11">
+        <f>Assumptions!B16*Assumptions!B17/1024*Assumptions!B18</f>
+        <v/>
+      </c>
+      <c r="C13" s="11">
+        <f>B13*12</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>C13*Assumptions!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>Subtotal — fixed platform (excl. AI)</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>SUM(B10:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="33">
+        <f>SUM(C10:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="34">
+        <f>SUM(D10:D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>AI / LLM usage (Claude)</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>B6*B7</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>B15*12</f>
+        <v/>
+      </c>
+      <c r="D15" s="12">
+        <f>C15*Assumptions!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL Replit (recurring)</t>
+        </is>
+      </c>
+      <c r="B16" s="15">
+        <f>B14+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="15">
+        <f>C14+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>D14+D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>One-time: process 100k books (month 1)</t>
+        </is>
+      </c>
+      <c r="B18" s="11">
+        <f>Assumptions!B19</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>B18*Assumptions!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>AI is by far the biggest cost. Cut it with answer caching, a cheaper model (Haiku) for simple questions, or free-tier limits.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1651,212 +1456,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>CTO Cost per Hour</t>
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Your Cost (CTO)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fully-loaded = salary × employer overhead. This is the true cost to the venture per CTO hour.</t>
+          <t>You are the only person on the project. This is what your time costs the venture.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>CTO monthly salary (BDT)</t>
-        </is>
-      </c>
-      <c r="B4" s="32">
-        <f>Team!B4</f>
+          <t>Your pay per month (BDT)</t>
+        </is>
+      </c>
+      <c r="B4" s="35">
+        <f>Assumptions!B25</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Working days per month</t>
+          <t>Working hours per month</t>
         </is>
       </c>
       <c r="B5" s="18">
-        <f>Assumptions!B22</f>
+        <f>Assumptions!B26*Assumptions!B27</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Working hours per day</t>
-        </is>
-      </c>
-      <c r="B6" s="18">
-        <f>Assumptions!B23</f>
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Cost per hour (BDT)</t>
+        </is>
+      </c>
+      <c r="B6" s="36">
+        <f>Assumptions!B25/B5</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Working hours per month</t>
-        </is>
-      </c>
-      <c r="B7" s="18">
-        <f>Assumptions!B22*Assumptions!B23</f>
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>Cost per hour (USD)</t>
+        </is>
+      </c>
+      <c r="B7" s="37">
+        <f>B6/Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Base cost per hour (BDT)</t>
-        </is>
-      </c>
-      <c r="B8" s="32">
-        <f>Team!B4/B7</f>
+          <t>Your pay per year (BDT)</t>
+        </is>
+      </c>
+      <c r="B8" s="35">
+        <f>Assumptions!B25*12</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>Fully-loaded cost per hour (BDT)</t>
-        </is>
-      </c>
-      <c r="B9" s="34">
-        <f>B8*Assumptions!B24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Base cost per hour (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="35">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Your pay per year (USD)</t>
+        </is>
+      </c>
+      <c r="B9" s="19">
         <f>B8/Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>Fully-loaded cost per hour (USD)</t>
-        </is>
-      </c>
-      <c r="B11" s="36">
-        <f>B9/Assumptions!B5</f>
-        <v/>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Your cost by engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>BDT</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>CTO cost by engagement (fully-loaded)</t>
-        </is>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Per hour</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C13" s="11">
+        <f>B6/Assumptions!B5</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>BDT</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Per day (8h)</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
+        <f>B6*Assumptions!B27</f>
+        <v/>
+      </c>
+      <c r="C14" s="11">
+        <f>B6*Assumptions!B27/Assumptions!B5</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per week (5 days)</t>
         </is>
       </c>
       <c r="B15" s="12">
-        <f>B9</f>
+        <f>B6*Assumptions!B27*5</f>
         <v/>
       </c>
       <c r="C15" s="11">
-        <f>B9/Assumptions!B5</f>
+        <f>B6*Assumptions!B27*5/Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Per day (8h)</t>
+          <t>Per month</t>
         </is>
       </c>
       <c r="B16" s="12">
-        <f>B9*Assumptions!B23</f>
+        <f>Assumptions!B25</f>
         <v/>
       </c>
       <c r="C16" s="11">
-        <f>B9*Assumptions!B23/Assumptions!B5</f>
+        <f>Assumptions!B25/Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Per week (5 days)</t>
+          <t>Per year</t>
         </is>
       </c>
       <c r="B17" s="12">
-        <f>B9*Assumptions!B23*5</f>
+        <f>Assumptions!B25*12</f>
         <v/>
       </c>
       <c r="C17" s="11">
-        <f>B9*Assumptions!B23*5/Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Per month</t>
-        </is>
-      </c>
-      <c r="B18" s="12">
-        <f>Team!B4*Assumptions!B24</f>
-        <v/>
-      </c>
-      <c r="C18" s="11">
-        <f>Team!B4*Assumptions!B24/Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Per year</t>
-        </is>
-      </c>
-      <c r="B19" s="12">
-        <f>Team!B4*Assumptions!B24*12</f>
-        <v/>
-      </c>
-      <c r="C19" s="11">
-        <f>Team!B4*Assumptions!B24*12/Assumptions!B5</f>
+        <f>Assumptions!B25*12/Assumptions!B5</f>
         <v/>
       </c>
     </row>
@@ -1871,513 +1654,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>AI / LLM Cost (Claude) — at full 1M scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>This is the steady-state run-rate assuming the full user target is active. The Timeline sheet ramps this up over the year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Monthly active users (MAU)</t>
-        </is>
-      </c>
-      <c r="B4" s="18">
-        <f>Assumptions!B7*Assumptions!B8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Queries per month</t>
-        </is>
-      </c>
-      <c r="B5" s="18">
-        <f>B4*Assumptions!B9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Queries per year</t>
-        </is>
-      </c>
-      <c r="B6" s="18">
-        <f>B5*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Cost per query (USD)</t>
-        </is>
-      </c>
-      <c r="B7" s="37">
-        <f>Assumptions!B11/1000000*Assumptions!B13+Assumptions!B12/1000000*Assumptions!B14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>LLM cost per month (USD)</t>
-        </is>
-      </c>
-      <c r="B8" s="38">
-        <f>B5*B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>LLM cost per year (USD)</t>
-        </is>
-      </c>
-      <c r="B9" s="39">
-        <f>B8*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>LLM cost per year (BDT)</t>
-        </is>
-      </c>
-      <c r="B10" s="34">
-        <f>B9*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Sensitivity — annual LLM cost by activity level</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Monthly active %</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>MAU</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Annual LLM (USD)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Annual LLM (BDT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B14" s="30">
-        <f>Assumptions!B7*A14</f>
-        <v/>
-      </c>
-      <c r="C14" s="11">
-        <f>B14*Assumptions!B9*12*B7</f>
-        <v/>
-      </c>
-      <c r="D14" s="12">
-        <f>C14*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B15" s="30">
-        <f>Assumptions!B7*A15</f>
-        <v/>
-      </c>
-      <c r="C15" s="11">
-        <f>B15*Assumptions!B9*12*B7</f>
-        <v/>
-      </c>
-      <c r="D15" s="12">
-        <f>C15*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B16" s="30">
-        <f>Assumptions!B7*A16</f>
-        <v/>
-      </c>
-      <c r="C16" s="11">
-        <f>B16*Assumptions!B9*12*B7</f>
-        <v/>
-      </c>
-      <c r="D16" s="12">
-        <f>C16*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>Levers to cut this: cache repeated answers, use a cheaper model (e.g. Haiku) for simple queries, cap free-tier usage.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Knowledge Integration — 100,000 books</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Storage + one-time ingestion. Human curation effort sits in the Team sheet (Knowledge-Ops Lead + Content Specialists).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Total storage (GB)</t>
-        </is>
-      </c>
-      <c r="B4" s="18">
-        <f>Assumptions!B16*Assumptions!B17/1024</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Total search chunks (info)</t>
-        </is>
-      </c>
-      <c r="B5" s="18">
-        <f>Assumptions!B16*Assumptions!B18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Storage cost per month (USD)</t>
-        </is>
-      </c>
-      <c r="B6" s="38">
-        <f>B4*Assumptions!B19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Storage cost per year (USD)</t>
-        </is>
-      </c>
-      <c r="B7" s="38">
-        <f>B6*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>One-time ingestion compute (USD)</t>
-        </is>
-      </c>
-      <c r="B8" s="38">
-        <f>Assumptions!B20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Year-1 knowledge cost (USD)</t>
-        </is>
-      </c>
-      <c r="B9" s="39">
-        <f>B7+B8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Run-rate annual knowledge cost (USD)</t>
-        </is>
-      </c>
-      <c r="B10" s="38">
-        <f>B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Year-1 knowledge cost (BDT)</t>
-        </is>
-      </c>
-      <c r="B11" s="32">
-        <f>B9*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Infrastructure (excl. AI &amp; knowledge storage)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Monthly (USD)</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Annual (USD)</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Annual (BDT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>App servers / hosting (autoscale)</t>
-        </is>
-      </c>
-      <c r="B4" s="11">
-        <f>Assumptions!B26</f>
-        <v/>
-      </c>
-      <c r="C4" s="11">
-        <f>B4*12</f>
-        <v/>
-      </c>
-      <c r="D4" s="12">
-        <f>C4*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>Managed PostgreSQL (scaled)</t>
-        </is>
-      </c>
-      <c r="B5" s="11">
-        <f>Assumptions!B27</f>
-        <v/>
-      </c>
-      <c r="C5" s="11">
-        <f>B5*12</f>
-        <v/>
-      </c>
-      <c r="D5" s="12">
-        <f>C5*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Bandwidth / CDN</t>
-        </is>
-      </c>
-      <c r="B6" s="11">
-        <f>Assumptions!B28</f>
-        <v/>
-      </c>
-      <c r="C6" s="11">
-        <f>B6*12</f>
-        <v/>
-      </c>
-      <c r="D6" s="12">
-        <f>C6*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Transactional email (Resend)</t>
-        </is>
-      </c>
-      <c r="B7" s="11">
-        <f>Assumptions!B29</f>
-        <v/>
-      </c>
-      <c r="C7" s="11">
-        <f>B7*12</f>
-        <v/>
-      </c>
-      <c r="D7" s="12">
-        <f>C7*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Monitoring / logging</t>
-        </is>
-      </c>
-      <c r="B8" s="11">
-        <f>Assumptions!B30</f>
-        <v/>
-      </c>
-      <c r="C8" s="11">
-        <f>B8*12</f>
-        <v/>
-      </c>
-      <c r="D8" s="12">
-        <f>C8*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Domain, SSL, misc SaaS</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
-        <f>Assumptions!B31</f>
-        <v/>
-      </c>
-      <c r="C9" s="11">
-        <f>B9*12</f>
-        <v/>
-      </c>
-      <c r="D9" s="12">
-        <f>C9*Assumptions!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="15">
-        <f>SUM(B4:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="15">
-        <f>SUM(C4:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="16">
-        <f>SUM(D4:D9)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -2386,7 +1669,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>12-Month Cash Timeline (with user ramp)</t>
         </is>
@@ -2395,7 +1678,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Active users ramp linearly to target by month 12. Team &amp; infra are fixed; ingestion one-time hits month 1.</t>
+          <t>Active users ramp up to target by month 12. Fixed Replit + your pay are constant; book processing hits month 1.</t>
         </is>
       </c>
     </row>
@@ -2412,22 +1695,22 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>LLM (USD)</t>
+          <t>AI (USD)</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>Infra (USD)</t>
+          <t>Replit fixed (USD)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Team (USD)</t>
+          <t>Your pay (USD)</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Knowledge (USD)</t>
+          <t>One-time (USD)</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
@@ -2450,24 +1733,24 @@
       <c r="A4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="38">
         <f>Assumptions!B7*Assumptions!B8*1/12</f>
         <v/>
       </c>
       <c r="C4" s="11">
-        <f>B4*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B4*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D4" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E4" s="11">
-        <f>Team!G13/12</f>
+        <f>Assumptions!B25/Assumptions!B5</f>
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>Knowledge!B6+Knowledge!B8</f>
+        <f>'Replit Costs'!B18</f>
         <v/>
       </c>
       <c r="G4" s="11">
@@ -2487,25 +1770,24 @@
       <c r="A5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="38">
         <f>Assumptions!B7*Assumptions!B8*2/12</f>
         <v/>
       </c>
       <c r="C5" s="11">
-        <f>B5*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B5*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D5" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="11">
         <f>C5+D5+E5+F5</f>
@@ -2524,25 +1806,24 @@
       <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="38">
         <f>Assumptions!B7*Assumptions!B8*3/12</f>
         <v/>
       </c>
       <c r="C6" s="11">
-        <f>B6*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B6*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D6" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E6" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F6" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="11">
         <f>C6+D6+E6+F6</f>
@@ -2561,25 +1842,24 @@
       <c r="A7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="38">
         <f>Assumptions!B7*Assumptions!B8*4/12</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>B7*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B7*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E7" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F7" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="11">
         <f>C7+D7+E7+F7</f>
@@ -2598,25 +1878,24 @@
       <c r="A8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="38">
         <f>Assumptions!B7*Assumptions!B8*5/12</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>B8*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B8*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F8" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="11">
         <f>C8+D8+E8+F8</f>
@@ -2635,25 +1914,24 @@
       <c r="A9" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="38">
         <f>Assumptions!B7*Assumptions!B8*6/12</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>B9*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B9*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F9" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="11">
         <f>C9+D9+E9+F9</f>
@@ -2672,25 +1950,24 @@
       <c r="A10" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="38">
         <f>Assumptions!B7*Assumptions!B8*7/12</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>B10*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B10*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G10" s="11">
         <f>C10+D10+E10+F10</f>
@@ -2709,25 +1986,24 @@
       <c r="A11" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="38">
         <f>Assumptions!B7*Assumptions!B8*8/12</f>
         <v/>
       </c>
       <c r="C11" s="11">
-        <f>B11*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B11*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D11" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E11" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="11">
         <f>C11+D11+E11+F11</f>
@@ -2746,25 +2022,24 @@
       <c r="A12" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="38">
         <f>Assumptions!B7*Assumptions!B8*9/12</f>
         <v/>
       </c>
       <c r="C12" s="11">
-        <f>B12*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B12*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D12" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E12" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F12" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="11">
         <f>C12+D12+E12+F12</f>
@@ -2783,25 +2058,24 @@
       <c r="A13" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="38">
         <f>Assumptions!B7*Assumptions!B8*10/12</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>B13*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B13*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E13" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F13" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G13" s="11">
         <f>C13+D13+E13+F13</f>
@@ -2820,25 +2094,24 @@
       <c r="A14" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="38">
         <f>Assumptions!B7*Assumptions!B8*11/12</f>
         <v/>
       </c>
       <c r="C14" s="11">
-        <f>B14*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B14*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D14" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E14" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F14" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="11">
         <f>C14+D14+E14+F14</f>
@@ -2857,25 +2130,24 @@
       <c r="A15" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="38">
         <f>Assumptions!B7*Assumptions!B8*12/12</f>
         <v/>
       </c>
       <c r="C15" s="11">
-        <f>B15*Assumptions!B9*'AI &amp; LLM'!B7</f>
+        <f>B15*Assumptions!B9*'Replit Costs'!B7</f>
         <v/>
       </c>
       <c r="D15" s="11">
-        <f>Infrastructure!B10</f>
+        <f>'Replit Costs'!B14</f>
         <v/>
       </c>
       <c r="E15" s="11">
-        <f>Team!G13/12</f>
-        <v/>
-      </c>
-      <c r="F15" s="11">
-        <f>Knowledge!B6</f>
-        <v/>
+        <f>Assumptions!B25/Assumptions!B5</f>
+        <v/>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="11">
         <f>C15+D15+E15+F15</f>
